--- a/results/tables/cluster_result.xlsx
+++ b/results/tables/cluster_result.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -647,7 +647,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -725,7 +725,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -842,7 +842,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="C11" t="n">
